--- a/hasil/rekap_error_gui.xlsx
+++ b/hasil/rekap_error_gui.xlsx
@@ -1,111 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="20">
-  <si>
-    <t>assignment_id</t>
-  </si>
-  <si>
-    <t>nama_usaha</t>
-  </si>
-  <si>
-    <t>sumber</t>
-  </si>
-  <si>
-    <t>baris</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>pesan</t>
-  </si>
-  <si>
-    <t>waktu</t>
-  </si>
-  <si>
-    <t>83dfb1d6-e935-431d-9435-2d7ac687b0a7</t>
-  </si>
-  <si>
-    <t>b6759b29-0153-4621-89f3-d6424d421786</t>
-  </si>
-  <si>
-    <t>d2d0b2ad-5fab-47b2-b5e1-e61305362aae</t>
-  </si>
-  <si>
-    <t>SPBU TITAN GRUP CIPEUCANG</t>
-  </si>
-  <si>
-    <t>SPBU PB SENTUL CITY</t>
-  </si>
-  <si>
-    <t>EUPHORBIA LANDSKAPE CV</t>
-  </si>
-  <si>
-    <t>C:/Users/Lenovo/OneDrive/Dokumen/KERJA/FASIH/OTOMASI/USAHA/DATA/G.xlsx</t>
-  </si>
-  <si>
-    <t>756</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>1345</t>
-  </si>
-  <si>
-    <t>error</t>
-  </si>
-  <si>
-    <t>Tahun operasi 2026 menurut G.xlsx; isian bulanan memerlukan penanganan khusus.</t>
-  </si>
-  <si>
-    <t>2026-10-19 07:44:09</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -113,36 +42,85 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -430,103 +408,508 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" t="s">
-        <v>19</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>assignment_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>nama_usaha</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>sumber</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>baris</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>pesan</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>waktu</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>83dfb1d6-e935-431d-9435-2d7ac687b0a7</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SPBU TITAN GRUP CIPEUCANG</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>C:/Users/Lenovo/OneDrive/Dokumen/KERJA/FASIH/OTOMASI/USAHA/DATA/G.xlsx</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>756</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Tahun operasi 2026 menurut G.xlsx; isian bulanan memerlukan penanganan khusus.</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-10-19 07:44:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>b6759b29-0153-4621-89f3-d6424d421786</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SPBU PB SENTUL CITY</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>C:/Users/Lenovo/OneDrive/Dokumen/KERJA/FASIH/OTOMASI/USAHA/DATA/G.xlsx</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tahun operasi 2026 menurut G.xlsx; isian bulanan memerlukan penanganan khusus.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-10-19 07:44:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>d2d0b2ad-5fab-47b2-b5e1-e61305362aae</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>EUPHORBIA LANDSKAPE CV</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>C:/Users/Lenovo/OneDrive/Dokumen/KERJA/FASIH/OTOMASI/USAHA/DATA/G.xlsx</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1345</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tahun operasi 2026 menurut G.xlsx; isian bulanan memerlukan penanganan khusus.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-10-19 07:44:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ad71b256-405f-41e6-b306-b7b7aa951430</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SRIKANDI DIAMOND MOTORS, PT</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>C:/Users/user/Downloads/G.xlsx</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Setelah Kirim, halaman review tidak sesuai assignment tujuan: https://fasih-sm.bps.go.id/app/assignment/37526b20-81c8-42f5-a895-6190137d7394/ad71b256-405f-41e6-b306-b7b7aa951430</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-10-19 08:59:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2506fb7d-60c7-48ea-9a44-976f4d523c86</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SPBU 344 13 52 / PT FELMICA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>C:/Users/user/Downloads/G.xlsx</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Locator.wait_for: Timeout 30000ms exceeded.
+Call log:
+  - waiting for get_by_role("alertdialog", name="Assignment Berhasil Disubmit") to be visible
+</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-10-19 09:00:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>4101ee41-5dd0-43cb-83ca-568761b04f0a</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PEMOTONGAN AYAM PD HZZE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>C:/Users/user/Downloads/G.xlsx</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Locator.wait_for: Target page, context or browser has been closed
+Call log:
+  - waiting for get_by_role("alertdialog", name="Assignment Berhasil Disubmit") to be visible
+</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-10-19 09:01:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>198b76af-8159-46c0-a3e2-e4de682cfb94</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PERTAMINA-PD SPBU 34-41328(PD SPBU 34-41328)PT </t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>C:/Users/user/Downloads/G.xlsx</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Locator.wait_for: Timeout 30000ms exceeded.
+Call log:
+  - waiting for locator("button:has(svg.tabler-icon-check):visible, button:has(svg.tabler-icon-rotate-clockwise):visible").first to be visible
+</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-10-19 09:05:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>604526b5-0da6-4b9b-b288-a67a0862adb2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>RAJA EMAS ID</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>C:/Users/user/Downloads/G.xlsx</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tahun operasi '2026' tidak didukung; isian bulanan perlu penanganan manual.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-10-19 09:05:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>891dc0d8-b931-4b55-a75f-2173d487ae5d</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SUKSES MANDIRI</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>C:/Users/user/Downloads/G.xlsx</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>GALAT validasi: Galat | TOTAL: 2 / 2 | 1 | SE2026 - L BLOK II | Perubahan Nama usaha/perusahaan Tulis perbaikan nama usaha, jika tidak ada perubahan tulis ulang nama usaha/perusahaan | Status badan usaha adalah CV maka nama usaha harus diakhiri dengan ,CV | 2 | CATATAN | Tampilkan Anomali Usaha dan Keluarga | Wajib diisi | Close</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-10-19 09:12:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>77ecde53-b8d8-4574-8015-082ba4afa240</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>TRI AMERTA SOLISINDO, PT</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>C:/Users/user/Downloads/G.xlsx</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>734</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tahun operasi '2026' tidak didukung; isian bulanan perlu penanganan manual.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-10-19 09:18:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>28600073-af17-44ab-9496-3e6d235d47f0</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>FAJAR KUMALA MOTOR, PT</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>C:/Users/user/Downloads/G.xlsx</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>781</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Setelah Kirim, halaman review tidak sesuai assignment tujuan: https://fasih-sm.bps.go.id/app/assignment/37526b20-81c8-42f5-a895-6190137d7394/28600073-af17-44ab-9496-3e6d235d47f0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-10-19 09:18:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>dcd7570e-4936-4efd-ada3-7c0e851365e1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>AKUR PRATAMA, PT</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>C:/Users/user/Downloads/G.xlsx</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Locator.wait_for: Timeout 30000ms exceeded.
+Call log:
+  - waiting for locator("button:has(svg.tabler-icon-rotate-clockwise):visible, button:has(svg.tabler-icon-edit):visible").first to be visible
+</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-10-20 04:15:36</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/hasil/rekap_error_gui.xlsx
+++ b/hasil/rekap_error_gui.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G592"/>
+  <dimension ref="A1:G602"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22368,6 +22368,379 @@
         </is>
       </c>
     </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>e7e2f6e3-3213-49ee-9112-43604a001373</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>MAJU LANCAR CV</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>DB:data_split_usaha_20261016</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>1114</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>Page.wait_for_function: Timeout 30000ms exceeded.</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>2026-10-23 03:58:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>7f5ae8d2-ec21-498c-9728-5db99d9e325d</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>AYAM UNGKEP KELILING DIAN LESMANA</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>DB:data_split_usaha_20261016</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>1138</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Locator.wait_for: Timeout 30000ms exceeded.
+Call log:
+  - waiting for locator("div.fasih-form-sidebar &gt; div[title=\"SE2026 - L BLOK II\"]:visible, div.fasih-form-sidebar &gt; div[title=\"BLOK I\"]:visible, div.fasih-form-sidebar &gt; div[title=\"BLOK II\"]:visible").first to be visible
+</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>2026-10-23 04:32:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>f4b288f3-49c9-4144-8539-e4123095d7e2</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>AYAM GEPREK BANG MALIK</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>DB:data_split_usaha_20261016</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>1318</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>Tahun operasi '2026' tidak didukung; isian bulanan perlu penanganan manual.</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>2026-10-23 04:49:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>bb04a5b7-c1dd-4749-ad83-bb3785a7f036</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>BU AISYAH</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>DB:data_split_usaha_20261016</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>1323</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>Tahun operasi '2026' tidak didukung; isian bulanan perlu penanganan manual.</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>2026-10-23 04:49:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>c656d2be-dd94-47e9-9ce6-9dfa99e0bfda</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>MENJUAL AYAM POTONG(HASANUDIN)</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>DB:data_split_usaha_20261016</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>1328</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>Tahun operasi '2026' tidak didukung; isian bulanan perlu penanganan manual.</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>2026-10-23 04:49:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>3eb7a7c4-b61f-4838-bf25-c6f063b8147b</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>USAHA AYAM POTONG AMIRUDIN</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>DB:data_split_usaha_20261016</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>1333</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>Tahun operasi '2026' tidak didukung; isian bulanan perlu penanganan manual.</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>2026-10-23 04:49:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>d53f3e48-e396-4417-979b-1aed0a339447</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>INTI YUDA SAMUDRA</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>DB:data_split_usaha_20261016</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>1363</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>Page.wait_for_function: Timeout 30000ms exceeded.</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>2026-10-23 04:53:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>bf7d9eba-bdae-402b-ae06-fefdafeffc0d</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>SURI NUSANTARA JAYA, PT</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>DB:data_split_usaha_20261016</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>1368</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>Tahun operasi '2026' tidak didukung; isian bulanan perlu penanganan manual.</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>2026-10-23 04:54:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>53c8c63e-6605-4f74-a25d-c54bdfbe7e52</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>PERIKANAN</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>DB:data_split_usaha_20261016</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>1398</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>Tahun operasi '2026' tidak didukung; isian bulanan perlu penanganan manual.</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>2026-10-23 04:55:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>b0cd5cfa-24cb-4967-ae0d-fc876bf13472</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>NESTARA TELUR (FAUZAN)</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>DB:data_split_usaha_20261016</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>1493</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>Tahun operasi '2026' tidak didukung; isian bulanan perlu penanganan manual.</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>2026-10-23 05:01:20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hasil/rekap_error_gui.xlsx
+++ b/hasil/rekap_error_gui.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G602"/>
+  <dimension ref="A1:G609"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22741,6 +22741,265 @@
         </is>
       </c>
     </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>161c2b74-1a43-44e7-8cae-f756f0895424</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>JUAL AYAM POTONG SAYUTI</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>DB:data_split_usaha_20261016</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>1326</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>Tahun operasi '2026' tidak didukung; isian bulanan perlu penanganan manual.</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:39:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>867dc247-6a0d-4e7f-8aad-20c424569e29</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>FROZEN FOOD (TRI JOKO PURNOMO)</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>DB:data_split_usaha_20261016</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>1551</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>Tahun operasi '2026' tidak didukung; isian bulanan perlu penanganan manual.</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:43:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>dffa3315-1549-4056-9c62-a532d9b29376</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>TOKO AL-GHIFARI</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>DB:data_split_usaha_20261016</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>1851</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>Tahun operasi '2026' tidak didukung; isian bulanan perlu penanganan manual.</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:46:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>77388f5e-05d2-4e44-9ed0-bf49eb802eed</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>DD AUTO MOBILINDO</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>DB:data_split_usaha_20261016</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>1901</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>Tahun operasi '2026' tidak didukung; isian bulanan perlu penanganan manual.</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:46:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>a8176203-88ea-4acb-a97e-b9a9effe5657</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TOKO BAHAN BANGUNAN </t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>DB:data_split_usaha_20261016</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>2926</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>Tahun operasi '2026' tidak didukung; isian bulanan perlu penanganan manual.</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:57:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>1d78c670-0f4d-403f-adb2-7b96c16e5aa3</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>CUCI PLASTIK (MAIN)</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>DB:data_split_usaha_20261016</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>3676</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>Tahun operasi '2026' tidak didukung; isian bulanan perlu penanganan manual.</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:06:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>a02a532b-4498-458a-820d-77eb36372e27</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>SORTIR RONGSOKAN (SAEFUL)</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>DB:data_split_usaha_20261016</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>3701</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>Tahun operasi '2026' tidak didukung; isian bulanan perlu penanganan manual.</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:06:26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
